--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DFS_HRM-2031-0332/Panel 7/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30103/BU01/HRM/post DFS_HRM-2031-0332/Panel 7/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,26 +456,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Pad Pos 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.78501</v>
+        <v>16.84364</v>
       </c>
       <c r="D2" t="n">
-        <v>16.60874</v>
+        <v>16.34299</v>
       </c>
       <c r="E2" t="n">
-        <v>16.53075</v>
+        <v>16.49914</v>
       </c>
       <c r="F2" t="n">
-        <v>42.1144</v>
+        <v>42.0377</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04949</v>
+        <v>0.05105</v>
       </c>
       <c r="H2" t="n">
-        <v>1.79659</v>
+        <v>1.79988</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.01699</v>
+        <v>16.96835</v>
       </c>
       <c r="D3" t="n">
-        <v>16.22414</v>
+        <v>16.43976</v>
       </c>
       <c r="E3" t="n">
-        <v>16.6319</v>
+        <v>16.4823</v>
       </c>
       <c r="F3" t="n">
-        <v>41.58163</v>
+        <v>42.38727</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05035</v>
+        <v>0.0508</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80951</v>
+        <v>1.79896</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.65902</v>
+        <v>16.78224</v>
       </c>
       <c r="D4" t="n">
-        <v>16.55764</v>
+        <v>16.57251</v>
       </c>
       <c r="E4" t="n">
-        <v>16.71604</v>
+        <v>16.62443</v>
       </c>
       <c r="F4" t="n">
-        <v>42.81931</v>
+        <v>42.08279</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05018</v>
+        <v>0.05072</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83741</v>
+        <v>1.83721</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.86011</v>
+        <v>16.61272</v>
       </c>
       <c r="D5" t="n">
-        <v>16.42789</v>
+        <v>16.5127</v>
       </c>
       <c r="E5" t="n">
-        <v>16.70701</v>
+        <v>16.54497</v>
       </c>
       <c r="F5" t="n">
-        <v>41.65386</v>
+        <v>43.02891</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05004</v>
+        <v>0.04949</v>
       </c>
       <c r="H5" t="n">
-        <v>1.80684</v>
+        <v>1.82022</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.63393</v>
+        <v>16.83067</v>
       </c>
       <c r="D6" t="n">
-        <v>16.71023</v>
+        <v>16.25542</v>
       </c>
       <c r="E6" t="n">
-        <v>16.68735</v>
+        <v>16.52572</v>
       </c>
       <c r="F6" t="n">
-        <v>42.39228</v>
+        <v>42.28797</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05001</v>
+        <v>0.05087</v>
       </c>
       <c r="H6" t="n">
-        <v>1.80196</v>
+        <v>1.81835</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.85246</v>
+        <v>16.69272</v>
       </c>
       <c r="D7" t="n">
-        <v>16.6571</v>
+        <v>16.53943</v>
       </c>
       <c r="E7" t="n">
-        <v>16.66449</v>
+        <v>16.59657</v>
       </c>
       <c r="F7" t="n">
-        <v>42.39399</v>
+        <v>42.06426</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05</v>
+        <v>0.04996</v>
       </c>
       <c r="H7" t="n">
-        <v>1.81918</v>
+        <v>1.83571</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.62102</v>
+        <v>16.74014</v>
       </c>
       <c r="D8" t="n">
-        <v>16.40467</v>
+        <v>16.55489</v>
       </c>
       <c r="E8" t="n">
-        <v>16.61972</v>
+        <v>16.72554</v>
       </c>
       <c r="F8" t="n">
-        <v>43.04725</v>
+        <v>42.72513</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0498</v>
+        <v>0.05056</v>
       </c>
       <c r="H8" t="n">
-        <v>1.80624</v>
+        <v>1.82465</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.59699</v>
+        <v>16.72505</v>
       </c>
       <c r="D9" t="n">
-        <v>16.57446</v>
+        <v>16.53544</v>
       </c>
       <c r="E9" t="n">
-        <v>16.06291</v>
+        <v>16.61076</v>
       </c>
       <c r="F9" t="n">
-        <v>42.71551</v>
+        <v>41.7679</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05062</v>
+        <v>0.05017</v>
       </c>
       <c r="H9" t="n">
-        <v>1.79789</v>
+        <v>1.83798</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.37604</v>
+        <v>16.60517</v>
       </c>
       <c r="D10" t="n">
-        <v>16.59067</v>
+        <v>16.27458</v>
       </c>
       <c r="E10" t="n">
-        <v>16.65039</v>
+        <v>16.51667</v>
       </c>
       <c r="F10" t="n">
-        <v>42.20526</v>
+        <v>42.12647</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05005</v>
+        <v>0.04957</v>
       </c>
       <c r="H10" t="n">
-        <v>1.81375</v>
+        <v>1.80943</v>
       </c>
     </row>
     <row r="11">
@@ -718,26 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad 2</t>
+          <t>Pad Pos 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.7368</v>
+        <v>16.66631</v>
       </c>
       <c r="D12" t="n">
-        <v>16.36334</v>
+        <v>16.59882</v>
       </c>
       <c r="E12" t="n">
-        <v>16.72821</v>
+        <v>16.63467</v>
       </c>
       <c r="F12" t="n">
-        <v>41.82675</v>
+        <v>42.97039</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05007</v>
+        <v>0.05097</v>
       </c>
       <c r="H12" t="n">
-        <v>1.81494</v>
+        <v>1.80726</v>
       </c>
     </row>
     <row r="13">
@@ -747,22 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.64352</v>
+        <v>16.57666</v>
       </c>
       <c r="D13" t="n">
-        <v>16.63381</v>
+        <v>16.18132</v>
       </c>
       <c r="E13" t="n">
-        <v>16.78684</v>
+        <v>16.51499</v>
       </c>
       <c r="F13" t="n">
-        <v>42.32795</v>
+        <v>42.09137</v>
       </c>
       <c r="G13" t="n">
-        <v>0.04948</v>
+        <v>0.04987</v>
       </c>
       <c r="H13" t="n">
-        <v>1.79449</v>
+        <v>1.78341</v>
       </c>
     </row>
     <row r="14">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.57249</v>
+        <v>16.77483</v>
       </c>
       <c r="D14" t="n">
-        <v>16.08316</v>
+        <v>16.49206</v>
       </c>
       <c r="E14" t="n">
-        <v>16.60652</v>
+        <v>16.74852</v>
       </c>
       <c r="F14" t="n">
-        <v>42.08856</v>
+        <v>42.32915</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05067</v>
+        <v>0.05079</v>
       </c>
       <c r="H14" t="n">
-        <v>1.82522</v>
+        <v>1.80104</v>
       </c>
     </row>
     <row r="15">
@@ -797,22 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.6571</v>
+        <v>16.92473</v>
       </c>
       <c r="D15" t="n">
-        <v>16.6927</v>
+        <v>16.39231</v>
       </c>
       <c r="E15" t="n">
-        <v>16.78608</v>
+        <v>16.60277</v>
       </c>
       <c r="F15" t="n">
-        <v>42.9089</v>
+        <v>42.0961</v>
       </c>
       <c r="G15" t="n">
-        <v>0.04955</v>
+        <v>0.05089</v>
       </c>
       <c r="H15" t="n">
-        <v>1.79055</v>
+        <v>1.81697</v>
       </c>
     </row>
     <row r="16">
@@ -822,22 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.69232</v>
+        <v>16.70716</v>
       </c>
       <c r="D16" t="n">
-        <v>16.46932</v>
+        <v>16.54886</v>
       </c>
       <c r="E16" t="n">
-        <v>16.65947</v>
+        <v>16.65991</v>
       </c>
       <c r="F16" t="n">
-        <v>42.41926</v>
+        <v>41.64675</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05054</v>
+        <v>0.05077</v>
       </c>
       <c r="H16" t="n">
-        <v>1.85637</v>
+        <v>1.81209</v>
       </c>
     </row>
     <row r="17">
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.86679</v>
+        <v>16.50698</v>
       </c>
       <c r="D17" t="n">
-        <v>16.31967</v>
+        <v>16.20026</v>
       </c>
       <c r="E17" t="n">
-        <v>16.58346</v>
+        <v>16.26365</v>
       </c>
       <c r="F17" t="n">
-        <v>42.05958</v>
+        <v>42.49841</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05034</v>
+        <v>0.05004</v>
       </c>
       <c r="H17" t="n">
-        <v>1.80345</v>
+        <v>1.80353</v>
       </c>
     </row>
     <row r="18">
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.54463</v>
+        <v>16.67227</v>
       </c>
       <c r="D18" t="n">
-        <v>16.51631</v>
+        <v>16.59738</v>
       </c>
       <c r="E18" t="n">
-        <v>16.39002</v>
+        <v>16.60443</v>
       </c>
       <c r="F18" t="n">
-        <v>42.29333</v>
+        <v>43.31984</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05053</v>
+        <v>0.04961</v>
       </c>
       <c r="H18" t="n">
-        <v>1.78952</v>
+        <v>1.80404</v>
       </c>
     </row>
     <row r="19">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.82069</v>
+        <v>16.85061</v>
       </c>
       <c r="D19" t="n">
-        <v>16.78959</v>
+        <v>16.54227</v>
       </c>
       <c r="E19" t="n">
-        <v>16.33736</v>
+        <v>16.59493</v>
       </c>
       <c r="F19" t="n">
-        <v>42.02905</v>
+        <v>43.07047</v>
       </c>
       <c r="G19" t="n">
-        <v>0.04967</v>
+        <v>0.05011</v>
       </c>
       <c r="H19" t="n">
-        <v>1.78182</v>
+        <v>1.83045</v>
       </c>
     </row>
     <row r="20">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.73396</v>
+        <v>16.95065</v>
       </c>
       <c r="D20" t="n">
-        <v>16.36871</v>
+        <v>16.37307</v>
       </c>
       <c r="E20" t="n">
-        <v>16.33204</v>
+        <v>16.56371</v>
       </c>
       <c r="F20" t="n">
-        <v>42.54964</v>
+        <v>42.76631</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05007</v>
+        <v>0.05142</v>
       </c>
       <c r="H20" t="n">
-        <v>1.82333</v>
+        <v>1.83262</v>
       </c>
     </row>
     <row r="21">
@@ -970,20 +970,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SR Pad 1</t>
+          <t>SR Pad Pos 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15.54779</v>
+        <v>15.64391</v>
       </c>
       <c r="D22" t="n">
-        <v>15.25782</v>
+        <v>15.44074</v>
       </c>
       <c r="E22" t="n">
-        <v>15.3997</v>
+        <v>15.58337</v>
       </c>
       <c r="F22" t="n">
-        <v>246.63213</v>
+        <v>252.58922</v>
       </c>
     </row>
     <row r="23">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15.70385</v>
+        <v>15.70755</v>
       </c>
       <c r="D23" t="n">
-        <v>15.74849</v>
+        <v>15.55936</v>
       </c>
       <c r="E23" t="n">
-        <v>15.4846</v>
+        <v>15.63636</v>
       </c>
       <c r="F23" t="n">
-        <v>255.08162</v>
+        <v>256.49695</v>
       </c>
     </row>
     <row r="24">
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>15.82982</v>
+        <v>15.77797</v>
       </c>
       <c r="D24" t="n">
-        <v>14.9651</v>
+        <v>15.36755</v>
       </c>
       <c r="E24" t="n">
-        <v>15.84423</v>
+        <v>15.62389</v>
       </c>
       <c r="F24" t="n">
-        <v>254.1351</v>
+        <v>256.7737</v>
       </c>
     </row>
     <row r="25">
@@ -1031,16 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>15.40071</v>
+        <v>15.66828</v>
       </c>
       <c r="D25" t="n">
-        <v>15.30366</v>
+        <v>15.53411</v>
       </c>
       <c r="E25" t="n">
-        <v>15.77259</v>
+        <v>15.55136</v>
       </c>
       <c r="F25" t="n">
-        <v>245.52304</v>
+        <v>250.10469</v>
       </c>
     </row>
     <row r="26">
@@ -1050,16 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>15.81062</v>
+        <v>15.56296</v>
       </c>
       <c r="D26" t="n">
-        <v>15.89308</v>
+        <v>15.30585</v>
       </c>
       <c r="E26" t="n">
-        <v>15.62885</v>
+        <v>15.50641</v>
       </c>
       <c r="F26" t="n">
-        <v>257.80945</v>
+        <v>249.0779</v>
       </c>
     </row>
     <row r="27">
@@ -1069,16 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>15.27059</v>
+        <v>15.51577</v>
       </c>
       <c r="D27" t="n">
-        <v>15.62245</v>
+        <v>15.1886</v>
       </c>
       <c r="E27" t="n">
-        <v>15.15778</v>
+        <v>15.34097</v>
       </c>
       <c r="F27" t="n">
-        <v>254.33945</v>
+        <v>247.10655</v>
       </c>
     </row>
     <row r="28">
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>15.54528</v>
+        <v>15.60215</v>
       </c>
       <c r="D28" t="n">
-        <v>15.33937</v>
+        <v>15.40573</v>
       </c>
       <c r="E28" t="n">
-        <v>15.35084</v>
+        <v>15.5175</v>
       </c>
       <c r="F28" t="n">
-        <v>246.85527</v>
+        <v>256.93875</v>
       </c>
     </row>
     <row r="29">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>15.39866</v>
+        <v>15.63169</v>
       </c>
       <c r="D29" t="n">
-        <v>15.18049</v>
+        <v>15.45344</v>
       </c>
       <c r="E29" t="n">
-        <v>15.58874</v>
+        <v>15.5062</v>
       </c>
       <c r="F29" t="n">
-        <v>252.1837</v>
+        <v>251.56812</v>
       </c>
     </row>
     <row r="30">
@@ -1126,16 +1126,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>15.53928</v>
+        <v>15.44819</v>
       </c>
       <c r="D30" t="n">
-        <v>15.471</v>
+        <v>15.32399</v>
       </c>
       <c r="E30" t="n">
-        <v>15.30497</v>
+        <v>15.37503</v>
       </c>
       <c r="F30" t="n">
-        <v>253.03438</v>
+        <v>255.69422</v>
       </c>
     </row>
     <row r="31">
@@ -1173,23 +1173,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>Trace Pos 1</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>16.62769</v>
+        <v>16.43615</v>
       </c>
       <c r="D32" t="n">
-        <v>16.06077</v>
+        <v>15.94798</v>
       </c>
       <c r="E32" t="n">
-        <v>16.46446</v>
+        <v>16.18485</v>
       </c>
       <c r="F32" t="n">
-        <v>21.35395</v>
+        <v>21.8185</v>
       </c>
       <c r="G32" t="n">
-        <v>34.20861</v>
+        <v>34.35743</v>
       </c>
     </row>
     <row r="33">
@@ -1199,19 +1199,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>16.9159</v>
+        <v>16.44863</v>
       </c>
       <c r="D33" t="n">
-        <v>16.035</v>
+        <v>15.66331</v>
       </c>
       <c r="E33" t="n">
-        <v>16.37474</v>
+        <v>16.19202</v>
       </c>
       <c r="F33" t="n">
-        <v>21.78191</v>
+        <v>21.53704</v>
       </c>
       <c r="G33" t="n">
-        <v>34.29581</v>
+        <v>33.7935</v>
       </c>
     </row>
     <row r="34">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>17.05165</v>
+        <v>16.50698</v>
       </c>
       <c r="D34" t="n">
-        <v>16.03212</v>
+        <v>16.1217</v>
       </c>
       <c r="E34" t="n">
-        <v>16.23781</v>
+        <v>16.31155</v>
       </c>
       <c r="F34" t="n">
-        <v>21.90432</v>
+        <v>21.45584</v>
       </c>
       <c r="G34" t="n">
-        <v>33.75847</v>
+        <v>34.4455</v>
       </c>
     </row>
     <row r="35">
@@ -1243,19 +1243,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>16.37741</v>
+        <v>16.42468</v>
       </c>
       <c r="D35" t="n">
-        <v>15.75193</v>
+        <v>16.23636</v>
       </c>
       <c r="E35" t="n">
-        <v>16.28369</v>
+        <v>16.38987</v>
       </c>
       <c r="F35" t="n">
-        <v>21.69677</v>
+        <v>21.84896</v>
       </c>
       <c r="G35" t="n">
-        <v>33.5491</v>
+        <v>34.19621</v>
       </c>
     </row>
     <row r="36">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>16.89248</v>
+        <v>16.88286</v>
       </c>
       <c r="D36" t="n">
-        <v>15.89167</v>
+        <v>15.71402</v>
       </c>
       <c r="E36" t="n">
-        <v>16.25075</v>
+        <v>16.5256</v>
       </c>
       <c r="F36" t="n">
-        <v>21.53147</v>
+        <v>21.26274</v>
       </c>
       <c r="G36" t="n">
-        <v>34.49553</v>
+        <v>34.26123</v>
       </c>
     </row>
     <row r="37">
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>16.91537</v>
+        <v>16.67921</v>
       </c>
       <c r="D37" t="n">
-        <v>15.79306</v>
+        <v>15.86405</v>
       </c>
       <c r="E37" t="n">
-        <v>16.38073</v>
+        <v>16.25349</v>
       </c>
       <c r="F37" t="n">
-        <v>21.61519</v>
+        <v>21.62135</v>
       </c>
       <c r="G37" t="n">
-        <v>34.34015</v>
+        <v>34.13367</v>
       </c>
     </row>
     <row r="38">
@@ -1309,19 +1309,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>16.58609</v>
+        <v>16.77341</v>
       </c>
       <c r="D38" t="n">
-        <v>16.06224</v>
+        <v>15.80074</v>
       </c>
       <c r="E38" t="n">
-        <v>16.11731</v>
+        <v>16.53768</v>
       </c>
       <c r="F38" t="n">
-        <v>22.08142</v>
+        <v>21.52258</v>
       </c>
       <c r="G38" t="n">
-        <v>33.79594</v>
+        <v>33.23372</v>
       </c>
     </row>
     <row r="39">
@@ -1331,19 +1331,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>16.2221</v>
+        <v>16.20986</v>
       </c>
       <c r="D39" t="n">
-        <v>15.98873</v>
+        <v>15.89175</v>
       </c>
       <c r="E39" t="n">
-        <v>16.31377</v>
+        <v>16.0834</v>
       </c>
       <c r="F39" t="n">
-        <v>21.60284</v>
+        <v>21.91304</v>
       </c>
       <c r="G39" t="n">
-        <v>34.31572</v>
+        <v>33.79535</v>
       </c>
     </row>
     <row r="40">
@@ -1353,45 +1353,30 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>16.61147</v>
+        <v>16.77107</v>
       </c>
       <c r="D40" t="n">
-        <v>15.90007</v>
+        <v>15.77467</v>
       </c>
       <c r="E40" t="n">
-        <v>16.72215</v>
+        <v>16.25469</v>
       </c>
       <c r="F40" t="n">
-        <v>21.69429</v>
+        <v>21.60235</v>
       </c>
       <c r="G40" t="n">
-        <v>33.96545</v>
+        <v>33.77589</v>
       </c>
     </row>
     <row r="41">
       <c r="C41" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Space</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -1403,23 +1388,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Trace 2</t>
+          <t>Via Pos 1</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>16.70852</v>
+        <v>0.60606</v>
       </c>
       <c r="D42" t="n">
-        <v>15.68115</v>
-      </c>
-      <c r="E42" t="n">
-        <v>16.32538</v>
-      </c>
-      <c r="F42" t="n">
-        <v>21.39106</v>
-      </c>
-      <c r="G42" t="n">
-        <v>34.30864</v>
+        <v>1.13135</v>
       </c>
     </row>
     <row r="43">
@@ -1429,19 +1405,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>16.78967</v>
+        <v>0.60631</v>
       </c>
       <c r="D43" t="n">
-        <v>16.07003</v>
-      </c>
-      <c r="E43" t="n">
-        <v>16.71226</v>
-      </c>
-      <c r="F43" t="n">
-        <v>22.05653</v>
-      </c>
-      <c r="G43" t="n">
-        <v>33.84043</v>
+        <v>1.10355</v>
       </c>
     </row>
     <row r="44">
@@ -1451,19 +1418,10 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>16.80155</v>
+        <v>0.60497</v>
       </c>
       <c r="D44" t="n">
-        <v>15.74494</v>
-      </c>
-      <c r="E44" t="n">
-        <v>16.32008</v>
-      </c>
-      <c r="F44" t="n">
-        <v>22.00531</v>
-      </c>
-      <c r="G44" t="n">
-        <v>33.61622</v>
+        <v>1.09187</v>
       </c>
     </row>
     <row r="45">
@@ -1473,19 +1431,10 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>16.66696</v>
+        <v>0.60027</v>
       </c>
       <c r="D45" t="n">
-        <v>15.59335</v>
-      </c>
-      <c r="E45" t="n">
-        <v>16.43295</v>
-      </c>
-      <c r="F45" t="n">
-        <v>21.33495</v>
-      </c>
-      <c r="G45" t="n">
-        <v>34.06572</v>
+        <v>1.0986</v>
       </c>
     </row>
     <row r="46">
@@ -1495,19 +1444,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>16.63972</v>
+        <v>0.59637</v>
       </c>
       <c r="D46" t="n">
-        <v>16.24914</v>
-      </c>
-      <c r="E46" t="n">
-        <v>16.15431</v>
-      </c>
-      <c r="F46" t="n">
-        <v>21.8469</v>
-      </c>
-      <c r="G46" t="n">
-        <v>34.28365</v>
+        <v>1.12201</v>
       </c>
     </row>
     <row r="47">
@@ -1517,19 +1457,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>16.80373</v>
+        <v>0.61147</v>
       </c>
       <c r="D47" t="n">
-        <v>15.82784</v>
-      </c>
-      <c r="E47" t="n">
-        <v>16.20507</v>
-      </c>
-      <c r="F47" t="n">
-        <v>21.48231</v>
-      </c>
-      <c r="G47" t="n">
-        <v>33.15903</v>
+        <v>1.10827</v>
       </c>
     </row>
     <row r="48">
@@ -1539,19 +1470,10 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>16.66733</v>
+        <v>0.59538</v>
       </c>
       <c r="D48" t="n">
-        <v>15.69377</v>
-      </c>
-      <c r="E48" t="n">
-        <v>16.32003</v>
-      </c>
-      <c r="F48" t="n">
-        <v>21.20846</v>
-      </c>
-      <c r="G48" t="n">
-        <v>34.53596</v>
+        <v>1.12434</v>
       </c>
     </row>
     <row r="49">
@@ -1561,19 +1483,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>16.7937</v>
+        <v>0.5912500000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>15.7631</v>
-      </c>
-      <c r="E49" t="n">
-        <v>16.36072</v>
-      </c>
-      <c r="F49" t="n">
-        <v>21.76633</v>
-      </c>
-      <c r="G49" t="n">
-        <v>33.4727</v>
+        <v>1.09248</v>
       </c>
     </row>
     <row r="50">
@@ -1583,30 +1496,31 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>16.8025</v>
+        <v>0.59365</v>
       </c>
       <c r="D50" t="n">
-        <v>15.66719</v>
-      </c>
-      <c r="E50" t="n">
-        <v>16.638</v>
-      </c>
-      <c r="F50" t="n">
-        <v>21.20577</v>
-      </c>
-      <c r="G50" t="n">
-        <v>33.8927</v>
+        <v>1.13609</v>
       </c>
     </row>
     <row r="51">
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dimple</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Bump</t>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Radius</t>
         </is>
       </c>
     </row>
@@ -1618,14 +1532,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>via 1</t>
+          <t>Landing Pad 1</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.60415</v>
+        <v>16.70759</v>
       </c>
       <c r="D52" t="n">
-        <v>1.11959</v>
+        <v>16.40385</v>
+      </c>
+      <c r="E52" t="n">
+        <v>16.53587</v>
+      </c>
+      <c r="F52" t="n">
+        <v>43.11078</v>
       </c>
     </row>
     <row r="53">
@@ -1635,10 +1555,16 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.61768</v>
+        <v>17.06056</v>
       </c>
       <c r="D53" t="n">
-        <v>1.08757</v>
+        <v>16.44478</v>
+      </c>
+      <c r="E53" t="n">
+        <v>16.83041</v>
+      </c>
+      <c r="F53" t="n">
+        <v>41.68673</v>
       </c>
     </row>
     <row r="54">
@@ -1648,10 +1574,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.60865</v>
+        <v>16.71001</v>
       </c>
       <c r="D54" t="n">
-        <v>1.12354</v>
+        <v>16.44282</v>
+      </c>
+      <c r="E54" t="n">
+        <v>16.58278</v>
+      </c>
+      <c r="F54" t="n">
+        <v>42.07827</v>
       </c>
     </row>
     <row r="55">
@@ -1661,10 +1593,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.61682</v>
+        <v>16.64521</v>
       </c>
       <c r="D55" t="n">
-        <v>1.10428</v>
+        <v>16.23233</v>
+      </c>
+      <c r="E55" t="n">
+        <v>16.46871</v>
+      </c>
+      <c r="F55" t="n">
+        <v>43.05504</v>
       </c>
     </row>
     <row r="56">
@@ -1674,10 +1612,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.60504</v>
+        <v>16.5311</v>
       </c>
       <c r="D56" t="n">
-        <v>1.08723</v>
+        <v>16.33564</v>
+      </c>
+      <c r="E56" t="n">
+        <v>16.42199</v>
+      </c>
+      <c r="F56" t="n">
+        <v>42.29364</v>
       </c>
     </row>
     <row r="57">
@@ -1687,10 +1631,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.60509</v>
+        <v>16.68773</v>
       </c>
       <c r="D57" t="n">
-        <v>1.11585</v>
+        <v>16.45831</v>
+      </c>
+      <c r="E57" t="n">
+        <v>16.6586</v>
+      </c>
+      <c r="F57" t="n">
+        <v>42.54992</v>
       </c>
     </row>
     <row r="58">
@@ -1700,10 +1650,16 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.60643</v>
+        <v>16.92382</v>
       </c>
       <c r="D58" t="n">
-        <v>1.10978</v>
+        <v>16.45888</v>
+      </c>
+      <c r="E58" t="n">
+        <v>16.84295</v>
+      </c>
+      <c r="F58" t="n">
+        <v>42.65811</v>
       </c>
     </row>
     <row r="59">
@@ -1713,10 +1669,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.60407</v>
+        <v>16.62823</v>
       </c>
       <c r="D59" t="n">
-        <v>1.08691</v>
+        <v>16.36401</v>
+      </c>
+      <c r="E59" t="n">
+        <v>16.60575</v>
+      </c>
+      <c r="F59" t="n">
+        <v>42.03104</v>
       </c>
     </row>
     <row r="60">
@@ -1726,144 +1688,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.60075</v>
+        <v>16.81212</v>
       </c>
       <c r="D60" t="n">
-        <v>1.06438</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>via 2</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>0.59476</v>
-      </c>
-      <c r="D62" t="n">
-        <v>1.11379</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Unit 8</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>0.60898</v>
-      </c>
-      <c r="D63" t="n">
-        <v>1.12481</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Unit 9</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>0.5984699999999999</v>
-      </c>
-      <c r="D64" t="n">
-        <v>1.11685</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Unit 4</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>0.59633</v>
-      </c>
-      <c r="D65" t="n">
-        <v>1.11828</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Unit 5</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>0.59702</v>
-      </c>
-      <c r="D66" t="n">
-        <v>1.1016</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Unit 6</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>0.60038</v>
-      </c>
-      <c r="D67" t="n">
-        <v>1.12567</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>0.59505</v>
-      </c>
-      <c r="D68" t="n">
-        <v>1.09856</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Unit 2</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>0.61312</v>
-      </c>
-      <c r="D69" t="n">
-        <v>1.11639</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Unit 3</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>0.6049</v>
-      </c>
-      <c r="D70" t="n">
-        <v>1.10005</v>
+        <v>16.43352</v>
+      </c>
+      <c r="E60" t="n">
+        <v>16.66306</v>
+      </c>
+      <c r="F60" t="n">
+        <v>42.47689</v>
       </c>
     </row>
   </sheetData>
